--- a/public/dc_inventory_template.xlsx
+++ b/public/dc_inventory_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kennethofili/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{510E6A56-5643-E04D-8312-F948357516B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60DB02A0-81B5-4B41-A2B9-34DE601DDBBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1580" yWindow="2000" windowWidth="26840" windowHeight="14640" xr2:uid="{0B5AF4B5-26C8-5849-A608-548BD1311F32}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Device / Label</t>
   </si>
@@ -62,6 +62,9 @@
   </si>
   <si>
     <t>UBA Tag Number</t>
+  </si>
+  <si>
+    <t>Deployment Date</t>
   </si>
 </sst>
 </file>
@@ -413,7 +416,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38ECAC49-A649-5742-AB57-3747544F9431}">
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -425,9 +428,10 @@
     <col min="7" max="7" width="23.33203125" customWidth="1"/>
     <col min="8" max="8" width="16.1640625" customWidth="1"/>
     <col min="9" max="9" width="22.83203125" customWidth="1"/>
+    <col min="10" max="10" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -454,6 +458,9 @@
       </c>
       <c r="I1" t="s">
         <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
